--- a/data/trans_orig/CoPsoQ-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2012</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>40770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>58538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74393</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101258</t>
+          <t>98388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42280</t>
+          <t>42602</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33635</t>
+          <t>33480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31713</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35219</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>60429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>206573</t>
+          <t>205666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>246883</t>
+          <t>245168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134952</t>
+          <t>134674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167150</t>
+          <t>168377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>351966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403068</t>
+          <t>401877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78844</t>
+          <t>78186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101450</t>
+          <t>103651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144320</t>
+          <t>143887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76559</t>
+          <t>77385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111917</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73535</t>
+          <t>74052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>130395</t>
+          <t>129666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175678</t>
+          <t>176367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>226740</t>
+          <t>227367</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266441</t>
+          <t>266780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139417</t>
+          <t>138460</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>172450</t>
+          <t>172137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>376628</t>
+          <t>378481</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>429674</t>
+          <t>432187</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56059</t>
+          <t>57287</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87523</t>
+          <t>89129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>46707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>74580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112293</t>
+          <t>109720</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154304</t>
+          <t>154590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77025</t>
+          <t>76191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111502</t>
+          <t>112679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47361</t>
+          <t>47235</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75211</t>
+          <t>74474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130937</t>
+          <t>132088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176886</t>
+          <t>177135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187176</t>
+          <t>186883</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228352</t>
+          <t>228745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95683</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128632</t>
+          <t>129574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294556</t>
+          <t>294604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>344257</t>
+          <t>345532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70911</t>
+          <t>69946</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107990</t>
+          <t>105911</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>33992</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59344</t>
+          <t>59348</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>111278</t>
+          <t>112678</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155084</t>
+          <t>156804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52660</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86823</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47968</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77701</t>
+          <t>75973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107624</t>
+          <t>106701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150091</t>
+          <t>150190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76026</t>
+          <t>76053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102320</t>
+          <t>101859</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106334</t>
+          <t>107173</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137538</t>
+          <t>138831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>43104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28929</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>39887</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>67550</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24173</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45174</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23412</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>36927</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>63356</t>
+          <t>62728</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>769749</t>
+          <t>774730</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>846847</t>
+          <t>848278</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>472183</t>
+          <t>469687</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>532756</t>
+          <t>534587</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1262592</t>
+          <t>1269457</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1362660</t>
+          <t>1370213</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>236265</t>
+          <t>240014</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>298568</t>
+          <t>300717</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>182765</t>
+          <t>181284</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>231805</t>
+          <t>232626</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>437644</t>
+          <t>432411</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>517798</t>
+          <t>513223</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>284968</t>
+          <t>280709</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>350336</t>
+          <t>345507</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>193059</t>
+          <t>195098</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>246162</t>
+          <t>245692</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>491825</t>
+          <t>490640</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>572755</t>
+          <t>576318</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2016</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47384</t>
+          <t>47732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43294</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61711</t>
+          <t>61304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77636</t>
+          <t>77141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104223</t>
+          <t>103234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>27385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>27995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>51033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>28944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31194</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>54267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178974</t>
+          <t>178593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216809</t>
+          <t>216974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,49 +6216,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>63,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>156572</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>141013</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>172416</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>62,99%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>156572</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>140681</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>173178</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>57,2%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>51,4%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>63,27%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>353</t>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331848</t>
+          <t>330112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>381461</t>
+          <t>379845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>63202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93434</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72326</t>
+          <t>72466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116526</t>
+          <t>116395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158238</t>
+          <t>155388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54889</t>
+          <t>52906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>84224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46311</t>
+          <t>45664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72656</t>
+          <t>72199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106982</t>
+          <t>107617</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>147305</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>237882</t>
+          <t>238662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>279555</t>
+          <t>281607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>156901</t>
+          <t>157864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>192191</t>
+          <t>193711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>404763</t>
+          <t>406304</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>461583</t>
+          <t>461509</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81339</t>
+          <t>81231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114541</t>
+          <t>115547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54755</t>
+          <t>53712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83844</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143985</t>
+          <t>143319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190894</t>
+          <t>191652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121495</t>
+          <t>122115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60651</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89057</t>
+          <t>89775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153810</t>
+          <t>155656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>201861</t>
+          <t>202560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172799</t>
+          <t>173294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213476</t>
+          <t>214791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115836</t>
+          <t>115941</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148789</t>
+          <t>149678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>301837</t>
+          <t>302256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352833</t>
+          <t>352919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>69856</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105292</t>
+          <t>104502</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44249</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>71337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122272</t>
+          <t>122212</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165876</t>
+          <t>165015</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71861</t>
+          <t>70643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105972</t>
+          <t>106432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>41123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69163</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119163</t>
+          <t>121832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164112</t>
+          <t>165123</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75486</t>
+          <t>74443</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102259</t>
+          <t>101619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41864</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63519</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124278</t>
+          <t>124047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158645</t>
+          <t>158619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>28232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>51706</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>34848</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47256</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77335</t>
+          <t>76602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27586</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>52409</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54230</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>84491</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>920</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9159,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9272,97 +9272,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>740569</t>
+          <t>745027</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>818182</t>
+          <t>821252</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>537174</t>
+          <t>540769</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>602263</t>
+          <t>602641</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1302964</t>
+          <t>1300916</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1407703</t>
+          <t>1401649</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>290444</t>
+          <t>289544</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>353247</t>
+          <t>353561</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>200413</t>
+          <t>199765</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>254134</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>501441</t>
+          <t>504803</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>590081</t>
+          <t>589018</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>289092</t>
+          <t>288229</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>356541</t>
+          <t>353114</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>216205</t>
+          <t>214666</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>270155</t>
+          <t>268141</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>513572</t>
+          <t>519414</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>602280</t>
+          <t>603912</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2023</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283977</t>
+          <t>279997</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>316363</t>
+          <t>315392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>221887</t>
+          <t>223074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245253</t>
+          <t>244588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>513746</t>
+          <t>516834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>556207</t>
+          <t>555017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43427</t>
+          <t>41033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40212</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>278578</t>
+          <t>278936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>325449</t>
+          <t>323004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>355487</t>
+          <t>355102</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>413378</t>
+          <t>413743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>649364</t>
+          <t>644294</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>723664</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56658</t>
+          <t>55940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>99174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>59056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79444</t>
+          <t>79710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42951</t>
+          <t>43810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70227</t>
+          <t>74640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>392807</t>
+          <t>393786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432082</t>
+          <t>433398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381447</t>
+          <t>381382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410780</t>
+          <t>410454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>783800</t>
+          <t>786445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>834550</t>
+          <t>834563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55900</t>
+          <t>56258</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67205</t>
+          <t>69245</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101009</t>
+          <t>102669</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>43958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69222</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>45948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>72010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>183494</t>
+          <t>225434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>689256</t>
+          <t>689945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>504212</t>
+          <t>503882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>542905</t>
+          <t>539959</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>593473</t>
+          <t>601165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1214818</t>
+          <t>1215097</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74701</t>
+          <t>71888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33967</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>56586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>51918</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>122228</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>38053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>19774</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>36895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68363</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65668</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642697</t>
+          <t>598960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>29541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49134</t>
+          <t>49326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101908</t>
+          <t>100423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>817872</t>
+          <t>793874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410371</t>
+          <t>411693</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>439201</t>
+          <t>439725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>413475</t>
+          <t>414310</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>431663</t>
+          <t>431736</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>834033</t>
+          <t>832889</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>867357</t>
+          <t>865806</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -12695,12 +12695,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40159</t>
+          <t>39423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>26922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>58776</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39612</t>
+          <t>41318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33434</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -13151,12 +13151,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>277971</t>
+          <t>277729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>283607</t>
+          <t>283495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>508013</t>
+          <t>507231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>518344</t>
+          <t>518337</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>788650</t>
+          <t>788613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>800928</t>
+          <t>801523</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>797</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>215945</t>
+          <t>215874</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>336596</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>337517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13770,12 +13770,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>553353</t>
+          <t>553398</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13996,12 +13996,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14109,12 +14109,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1841028</t>
+          <t>1848070</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2652915</t>
+          <t>2659127</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2759991</t>
+          <t>2761894</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2881710</t>
+          <t>2873844</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4503499</t>
+          <t>4490991</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5477779</t>
+          <t>5481471</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>126291</t>
+          <t>126552</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>198900</t>
+          <t>199545</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>126599</t>
+          <t>127200</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>186795</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>272556</t>
+          <t>276505</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>367136</t>
+          <t>372829</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>89689</t>
+          <t>85348</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>149790</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>102330</t>
+          <t>100828</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>168305</t>
+          <t>172523</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>239405</t>
+          <t>238420</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>140378</t>
+          <t>138693</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1038337</t>
+          <t>1035544</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>80523</t>
+          <t>83290</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128698</t>
+          <t>128814</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>241897</t>
+          <t>236994</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1301515</t>
+          <t>1295377</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoPsoQ-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Edad-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>46420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>40017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58538</t>
+          <t>59842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73173</t>
+          <t>72718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98388</t>
+          <t>99489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,8%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22462</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33480</t>
+          <t>33766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37018</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60429</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>205666</t>
+          <t>205734</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>245168</t>
+          <t>244949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134674</t>
+          <t>131960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168377</t>
+          <t>169124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351966</t>
+          <t>350354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>401877</t>
+          <t>402945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,71%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>74670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50879</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78186</t>
+          <t>79182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103651</t>
+          <t>102714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143887</t>
+          <t>144341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>79898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113086</t>
+          <t>114509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>44108</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129666</t>
+          <t>131668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176367</t>
+          <t>178231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>227367</t>
+          <t>229084</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266780</t>
+          <t>269096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138460</t>
+          <t>139601</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>172137</t>
+          <t>172250</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>378481</t>
+          <t>377919</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>432187</t>
+          <t>430107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57287</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>47345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74580</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109720</t>
+          <t>113045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154590</t>
+          <t>155078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76191</t>
+          <t>75181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>110834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47235</t>
+          <t>48189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>76210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132088</t>
+          <t>133194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177135</t>
+          <t>177258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186883</t>
+          <t>186009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228745</t>
+          <t>226569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>96706</t>
+          <t>96746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129574</t>
+          <t>127883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294604</t>
+          <t>293970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345532</t>
+          <t>346923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69946</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105911</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59348</t>
+          <t>58280</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>112678</t>
+          <t>110989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>156804</t>
+          <t>156981</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52284</t>
+          <t>53001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84143</t>
+          <t>83840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>47080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75973</t>
+          <t>76743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>107636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150190</t>
+          <t>153954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>76091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101859</t>
+          <t>101919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107173</t>
+          <t>106403</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138831</t>
+          <t>137702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,5%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43104</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67550</t>
+          <t>66836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>46651</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>36927</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>62728</t>
+          <t>63022</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>774730</t>
+          <t>767735</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>848278</t>
+          <t>844525</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>469687</t>
+          <t>470536</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>534587</t>
+          <t>534354</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1269457</t>
+          <t>1265943</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1370213</t>
+          <t>1364162</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>240014</t>
+          <t>238459</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>300717</t>
+          <t>300433</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>181284</t>
+          <t>183497</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>232626</t>
+          <t>235905</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>432411</t>
+          <t>434119</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>513223</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>280709</t>
+          <t>284308</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>345507</t>
+          <t>350478</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>195098</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>245692</t>
+          <t>245807</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>490640</t>
+          <t>490964</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>576318</t>
+          <t>571919</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>28890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47732</t>
+          <t>47082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>43388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>61902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77141</t>
+          <t>76248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103234</t>
+          <t>103594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>31934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178593</t>
+          <t>178993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216974</t>
+          <t>215676</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141013</t>
+          <t>140600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172416</t>
+          <t>171574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330112</t>
+          <t>327156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379845</t>
+          <t>375657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63202</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96131</t>
+          <t>95348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46399</t>
+          <t>45505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72466</t>
+          <t>70774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116395</t>
+          <t>115764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155388</t>
+          <t>157071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52906</t>
+          <t>55698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84224</t>
+          <t>85138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45664</t>
+          <t>46697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72199</t>
+          <t>72807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107617</t>
+          <t>107906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>147484</t>
+          <t>149719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>238662</t>
+          <t>237380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281607</t>
+          <t>278955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>157864</t>
+          <t>158180</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>193711</t>
+          <t>192955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>406304</t>
+          <t>408191</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>461509</t>
+          <t>462651</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81231</t>
+          <t>79446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115547</t>
+          <t>114311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53712</t>
+          <t>55265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84261</t>
+          <t>84346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143319</t>
+          <t>143301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191652</t>
+          <t>189624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>86333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122115</t>
+          <t>121979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59321</t>
+          <t>60295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89775</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155656</t>
+          <t>155860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202560</t>
+          <t>202390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173294</t>
+          <t>176431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214791</t>
+          <t>215322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>116721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>149678</t>
+          <t>146617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302256</t>
+          <t>300189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352919</t>
+          <t>350950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69856</t>
+          <t>69358</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104502</t>
+          <t>104297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71337</t>
+          <t>69530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122212</t>
+          <t>121798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165015</t>
+          <t>165681</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70643</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106432</t>
+          <t>106005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41123</t>
+          <t>42324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68357</t>
+          <t>70029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121832</t>
+          <t>120631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165123</t>
+          <t>163493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74443</t>
+          <t>75487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>102205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64448</t>
+          <t>64237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124047</t>
+          <t>124000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158619</t>
+          <t>158615</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>28479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51706</t>
+          <t>51035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34848</t>
+          <t>34022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47190</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76602</t>
+          <t>77933</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54954</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84491</t>
+          <t>85489</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>741230</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>821252</t>
+          <t>819477</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>540769</t>
+          <t>540879</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>602641</t>
+          <t>604002</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1300916</t>
+          <t>1304801</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1401649</t>
+          <t>1404483</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>289544</t>
+          <t>287833</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>353561</t>
+          <t>355907</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>201273</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>254134</t>
+          <t>251522</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>504803</t>
+          <t>508623</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>589018</t>
+          <t>593410</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>288229</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>353114</t>
+          <t>353064</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>214666</t>
+          <t>213218</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>268141</t>
+          <t>270388</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>519414</t>
+          <t>519396</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>603912</t>
+          <t>602496</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -10301,32 +10301,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>303665</t>
+          <t>309651</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279997</t>
+          <t>289322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>315392</t>
+          <t>323499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10336,32 +10336,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>235928</t>
+          <t>270883</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223074</t>
+          <t>256458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244588</t>
+          <t>281776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10371,32 +10371,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>539593</t>
+          <t>580535</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>516834</t>
+          <t>553789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>555017</t>
+          <t>597077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -10414,32 +10414,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27972</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10449,32 +10449,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10484,32 +10484,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>29751</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -10537,12 +10537,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10562,32 +10562,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10597,32 +10597,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -10640,32 +10640,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10675,32 +10675,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10710,32 +10710,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36468</t>
+          <t>35087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -10753,17 +10753,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>327057</t>
+          <t>339756</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>327057</t>
+          <t>339756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327057</t>
+          <t>339756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10788,17 +10788,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>259182</t>
+          <t>297324</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>259182</t>
+          <t>297324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259182</t>
+          <t>297324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10823,17 +10823,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>586239</t>
+          <t>637080</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>586239</t>
+          <t>637080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>586239</t>
+          <t>637080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10870,32 +10870,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>302144</t>
+          <t>341468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>278936</t>
+          <t>316987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323004</t>
+          <t>364789</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10905,32 +10905,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377542</t>
+          <t>348160</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>355102</t>
+          <t>328089</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>413743</t>
+          <t>364979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10940,32 +10940,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>679686</t>
+          <t>689629</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>644294</t>
+          <t>656697</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>723664</t>
+          <t>717468</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -10983,32 +10983,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>30565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55940</t>
+          <t>67307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11018,32 +11018,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36411</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>52216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11053,32 +11053,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>75362</t>
+          <t>86005</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55488</t>
+          <t>67062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99174</t>
+          <t>109972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -11096,32 +11096,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59056</t>
+          <t>61971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11131,32 +11131,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28228</t>
+          <t>35354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11166,32 +11166,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59871</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>49674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79710</t>
+          <t>88229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -11209,32 +11209,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43810</t>
+          <t>45692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11244,32 +11244,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>41269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11279,32 +11279,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>52401</t>
+          <t>56938</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>41277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74640</t>
+          <t>79173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -11322,17 +11322,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>460009</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>460009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>460009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11357,17 +11357,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>458122</t>
+          <t>439932</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>458122</t>
+          <t>439932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>458122</t>
+          <t>439932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11392,17 +11392,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>867319</t>
+          <t>899941</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>867319</t>
+          <t>899941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>867319</t>
+          <t>899941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11439,32 +11439,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>414547</t>
+          <t>480698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>393786</t>
+          <t>457742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433398</t>
+          <t>498282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11474,32 +11474,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>396763</t>
+          <t>457852</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381382</t>
+          <t>440079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410454</t>
+          <t>473057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11509,32 +11509,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>811310</t>
+          <t>938550</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>786445</t>
+          <t>910174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>834563</t>
+          <t>962947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11552,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27897</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>61019</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11587,32 +11587,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43941</t>
+          <t>51341</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>40630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11622,32 +11622,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>83072</t>
+          <t>96158</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69245</t>
+          <t>77914</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>114833</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -11665,32 +11665,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43958</t>
+          <t>50267</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11700,32 +11700,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>17603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11735,32 +11735,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>60362</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>76916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -11778,32 +11778,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>52444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11813,32 +11813,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>37789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11848,32 +11848,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>57289</t>
+          <t>65453</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44469</t>
+          <t>51414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72010</t>
+          <t>84764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -11891,17 +11891,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>516633</t>
+          <t>598692</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>516633</t>
+          <t>598692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>516633</t>
+          <t>598692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11926,17 +11926,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>489002</t>
+          <t>561831</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>489002</t>
+          <t>561831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>489002</t>
+          <t>561831</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11961,17 +11961,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1005635</t>
+          <t>1160523</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1005635</t>
+          <t>1160523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1005635</t>
+          <t>1160523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>486668</t>
+          <t>523961</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>225434</t>
+          <t>499867</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>689945</t>
+          <t>543236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>520812</t>
+          <t>529111</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>503882</t>
+          <t>513177</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>539959</t>
+          <t>543464</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1007480</t>
+          <t>1053073</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>601165</t>
+          <t>1025273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1215097</t>
+          <t>1078713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -12121,32 +12121,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>50973</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>38872</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>65809</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12156,32 +12156,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45407</t>
+          <t>49805</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56586</t>
+          <t>61560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12191,32 +12191,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>93186</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51918</t>
+          <t>85135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122228</t>
+          <t>118988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -12234,32 +12234,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38053</t>
+          <t>39149</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12269,32 +12269,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36895</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12304,32 +12304,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67731</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -12347,32 +12347,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>295308</t>
+          <t>59856</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65356</t>
+          <t>45726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>598960</t>
+          <t>76608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12382,32 +12382,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38702</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49326</t>
+          <t>54122</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12417,32 +12417,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>334009</t>
+          <t>102265</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100423</t>
+          <t>84730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>793874</t>
+          <t>121259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -12460,17 +12460,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>853838</t>
+          <t>661133</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>853838</t>
+          <t>661133</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>853838</t>
+          <t>661133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12495,17 +12495,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>631752</t>
+          <t>649864</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>631752</t>
+          <t>649864</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631752</t>
+          <t>649864</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12530,17 +12530,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1485590</t>
+          <t>1310997</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1485590</t>
+          <t>1310997</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1485590</t>
+          <t>1310997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>426324</t>
+          <t>464669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>411693</t>
+          <t>447405</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>439725</t>
+          <t>478433</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424135</t>
+          <t>472162</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>414310</t>
+          <t>462423</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>431736</t>
+          <t>481061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>850460</t>
+          <t>936831</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>832889</t>
+          <t>918698</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>865806</t>
+          <t>953061</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -12690,32 +12690,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>43057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12725,27 +12725,27 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -12760,27 +12760,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58776</t>
+          <t>64529</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12803,32 +12803,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12838,32 +12838,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12873,32 +12873,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>29591</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41318</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12951,32 +12951,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12986,32 +12986,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>33434</t>
+          <t>38251</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -13029,17 +13029,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>491162</t>
+          <t>533267</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>491162</t>
+          <t>533267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>491162</t>
+          <t>533267</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13064,17 +13064,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>460935</t>
+          <t>513210</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>460935</t>
+          <t>513210</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>460935</t>
+          <t>513210</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>952097</t>
+          <t>1046477</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>952097</t>
+          <t>1046477</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>952097</t>
+          <t>1046477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>281399</t>
+          <t>311283</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>277729</t>
+          <t>307340</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>283495</t>
+          <t>313526</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13181,32 +13181,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>513650</t>
+          <t>336933</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>507231</t>
+          <t>332334</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>518337</t>
+          <t>339799</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>795049</t>
+          <t>648216</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>788613</t>
+          <t>642553</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>801523</t>
+          <t>651970</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -13304,12 +13304,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13329,32 +13329,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13407,32 +13407,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13442,32 +13442,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13520,32 +13520,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13555,32 +13555,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -13598,17 +13598,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>284941</t>
+          <t>314904</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>284941</t>
+          <t>314904</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>284941</t>
+          <t>314904</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13633,17 +13633,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>519723</t>
+          <t>343261</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>519723</t>
+          <t>343261</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>519723</t>
+          <t>343261</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13668,17 +13668,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>804664</t>
+          <t>658165</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>804664</t>
+          <t>658165</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>804664</t>
+          <t>658165</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13715,27 +13715,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>218874</t>
+          <t>241151</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>215874</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>219620</t>
+          <t>242038</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>337517</t>
+          <t>366965</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -13785,27 +13785,27 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>556391</t>
+          <t>608116</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>553398</t>
+          <t>604518</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>557137</t>
+          <t>609003</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -14134,12 +14134,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -14167,17 +14167,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>219620</t>
+          <t>242038</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>219620</t>
+          <t>242038</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>219620</t>
+          <t>242038</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14202,17 +14202,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>337517</t>
+          <t>366965</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>337517</t>
+          <t>366965</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>337517</t>
+          <t>366965</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14237,17 +14237,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>557137</t>
+          <t>609003</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>557137</t>
+          <t>609003</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>557137</t>
+          <t>609003</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2433622</t>
+          <t>2672882</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1848070</t>
+          <t>2625824</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2659127</t>
+          <t>2718744</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2806345</t>
+          <t>2782065</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2761894</t>
+          <t>2748091</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2873844</t>
+          <t>2814892</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>5239968</t>
+          <t>5454948</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4490991</t>
+          <t>5393247</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5481471</t>
+          <t>5509344</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -14397,32 +14397,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>166193</t>
+          <t>189040</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>159160</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>199545</t>
+          <t>220265</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14432,32 +14432,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>159664</t>
+          <t>178084</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>156019</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>186388</t>
+          <t>202712</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14467,32 +14467,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>325857</t>
+          <t>367125</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>276505</t>
+          <t>331380</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>372829</t>
+          <t>412395</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -14510,32 +14510,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>108909</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14545,32 +14545,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>83729</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>63787</t>
+          <t>78682</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>100828</t>
+          <t>112553</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14580,32 +14580,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>204845</t>
+          <t>225769</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>199287</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>238420</t>
+          <t>256636</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -14623,32 +14623,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>381516</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>138693</t>
+          <t>128852</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1035544</t>
+          <t>191559</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14658,32 +14658,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>106493</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>83290</t>
+          <t>99873</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128814</t>
+          <t>139077</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14693,32 +14693,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>488010</t>
+          <t>274343</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>241745</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1295377</t>
+          <t>311088</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -14736,17 +14736,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14771,17 +14771,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14806,17 +14806,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
